--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031389</v>
+        <v>125031386</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6990156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031384</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R3" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031384</v>
+        <v>125031389</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R4" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031386</v>
+        <v>125031389</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6990156</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031384</v>
+        <v>125031388</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R3" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031389</v>
+        <v>125031386</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
         <v>6990156</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R5" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031388</v>
+        <v>125031386</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031386</v>
+        <v>125031388</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
         <v>6990156</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031389</v>
+        <v>125031388</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031389</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R4" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031384</v>
+        <v>125031386</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R5" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R2" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031389</v>
+        <v>125031386</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031384</v>
+        <v>125031389</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R4" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031386</v>
+        <v>125031388</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
         <v>6990156</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031384</v>
+        <v>125031388</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R2" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031384</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R3" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031389</v>
+        <v>125031386</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
         <v>6990156</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031388</v>
+        <v>125031389</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R2" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031384</v>
+        <v>125031386</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R3" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031386</v>
+        <v>125031388</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
         <v>6990156</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031384</v>
+        <v>125031388</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R2" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R4" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R2" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031389</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031384</v>
+        <v>125031386</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R4" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031389</v>
+        <v>125031388</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031384</v>
+        <v>125031388</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R2" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031389</v>
+        <v>125031386</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031386</v>
+        <v>125031384</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R4" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031388</v>
+        <v>125031389</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031388</v>
+        <v>125031386</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>56828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6990156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031384</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R3" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031384</v>
+        <v>125031389</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>91459</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R4" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031389</v>
+        <v>125031388</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031386</v>
+        <v>125031384</v>
       </c>
       <c r="B2" t="n">
-        <v>56828</v>
+        <v>92448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R2" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031384</v>
+        <v>125031386</v>
       </c>
       <c r="B3" t="n">
-        <v>92448</v>
+        <v>56828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R3" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031389</v>
+        <v>125031388</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
+        <v>91166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125031388</v>
+        <v>125031389</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 20519-2024 artfynd.xlsx
+++ b/artfynd/A 20519-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125031384</v>
+        <v>125031386</v>
       </c>
       <c r="B2" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622685</v>
+        <v>622735</v>
       </c>
       <c r="R2" t="n">
-        <v>6990173</v>
+        <v>6990156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125031386</v>
+        <v>125031388</v>
       </c>
       <c r="B3" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +813,7 @@
         <v>6990156</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125031388</v>
+        <v>125031384</v>
       </c>
       <c r="B4" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622735</v>
+        <v>622685</v>
       </c>
       <c r="R4" t="n">
-        <v>6990156</v>
+        <v>6990173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,11 +970,6 @@
       </c>
       <c r="B5" t="n">
         <v>91459</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
